--- a/tahoho/example/cowork-needs-folder/訓練安排.xlsx
+++ b/tahoho/example/cowork-needs-folder/訓練安排.xlsx
@@ -1,69 +1,173 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\910276\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A02D364C-4697-49F9-8A86-3FE83E490711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{24942ACF-9C28-451A-8EF8-213AF01DABBA}"/>
   </bookViews>
   <sheets>
-    <sheet name="課程明細" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="課程明細" sheetId="5" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
+  <si>
+    <t>T</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BCG問題解決力3：AI導入的高效決策</t>
+  </si>
+  <si>
+    <t>AI轉型全攻略｜企業第一個AI專案｜從執行到覆盤的系統化解方</t>
+  </si>
+  <si>
+    <t>AI轉型全攻略｜+AI商業應用解題｜掌握AI底層邏輯創造商業價值</t>
+  </si>
+  <si>
+    <t>AI轉型全攻略｜企業AI工作流再造｜實現商業價值最大化</t>
+  </si>
+  <si>
+    <t>AI轉型全攻略｜打造 AI Agent 應用藍圖｜從構想到落地的行動指南</t>
+  </si>
+  <si>
+    <t>J</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>天下學習-銷售的修煉：從自我成長到客戶成功的業務哲學</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>天下學習-高效溝通：正向對話、化解衝突、創造共識｜七大法則解決所有難題</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>天下學習-帶心管理學：降低離職率，創造高績效 (李河泉)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>天下學習-Midee的溝通談判課：從對立到共贏(Midee 陳淑芬)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>姓名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>林凱瑞</t>
+  </si>
+  <si>
+    <t>蘇嘉宏</t>
+  </si>
+  <si>
+    <t>茅士強</t>
+  </si>
+  <si>
+    <t>楊昇淮</t>
+  </si>
+  <si>
+    <t>黃信行</t>
+  </si>
+  <si>
+    <t>李敏菁</t>
+  </si>
+  <si>
+    <t>胡立華</t>
+  </si>
+  <si>
+    <t>楊芳哲</t>
+  </si>
+  <si>
+    <t>序號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>tina.fan</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jessica</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="新細明體"/>
+      <family val="2"/>
       <charset val="136"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="微軟正黑體"/>
+      <family val="2"/>
       <charset val="136"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="新細明體"/>
+      <family val="2"/>
       <charset val="136"/>
-      <family val="2"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF4A4A4A"/>
       <name val="微軟正黑體"/>
+      <family val="2"/>
       <charset val="136"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF4A4A4A"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="微軟正黑體"/>
+      <family val="2"/>
       <charset val="136"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -119,111 +223,52 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -543,269 +588,202 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E1648C9-E494-4FFE-ACED-3888264BF74C}">
   <dimension ref="B1:F20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="9" customWidth="1" style="4" min="3" max="3"/>
-    <col width="77.25" bestFit="1" customWidth="1" style="4" min="4" max="4"/>
-    <col width="9" customWidth="1" style="3" min="5" max="6"/>
+    <col min="3" max="3" width="9" style="4"/>
+    <col min="4" max="4" width="77.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t>帳號A</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>序號</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="D2" s="6" t="n"/>
-      <c r="E2" s="1" t="n">
+    <row r="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D2" s="6"/>
+      <c r="E2" s="1">
         <v>1</v>
       </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>陳怡君</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>AI 問題解決力：AI 導入的高效決策</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="n">
+      <c r="F2" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
         <v>2</v>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>王志明</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>AI 轉型全攻略｜企業第一個 AI 專案</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="n">
+      <c r="F3" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="1">
         <v>3</v>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>林雅婷</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>AI 轉型全攻略｜AI 商業應用解題</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="n">
+      <c r="F4" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1">
         <v>4</v>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>張家豪</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>AI 轉型全攻略｜企業 AI 工作流再造</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="n">
+      <c r="F5" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1">
         <v>5</v>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>李佳穎</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>AI 轉型全攻略｜打造 AI Agent 應用藍圖</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="n">
+      <c r="F6" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C7" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="1">
         <v>6</v>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>黃冠宇</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="1" t="n">
+      <c r="F7" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D8" s="6"/>
+      <c r="E8" s="1">
         <v>7</v>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>吳宗翰</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="1" t="n">
+      <c r="F8" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D9" s="7"/>
+      <c r="E9" s="1">
         <v>8</v>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>劉淑芬</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="E10" s="1" t="n"/>
-      <c r="F10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="E11" s="1" t="n"/>
-      <c r="F11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="E12" s="1" t="n"/>
-      <c r="F12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="0" t="inlineStr">
-        <is>
-          <t>帳號B</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>銷售的修煉：從自我成長到客戶成功</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="n"/>
-      <c r="F13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>高效溝通：正向對話、化解衝突、創造共識</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="n"/>
-      <c r="F14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>銷售的修煉：從自我成長到客戶成功</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="n"/>
-      <c r="F15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>帶心管理學：降低離職率，創造高績效</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="n"/>
-      <c r="F16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>溝通談判課：從對立到共贏</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="n"/>
-      <c r="F17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="E18" s="1" t="n"/>
-      <c r="F18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="E19" s="1" t="n"/>
-      <c r="F19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="E20" s="1" t="n"/>
-      <c r="F20" s="5" t="n"/>
+      <c r="F9" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="E10" s="1"/>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="E11" s="1"/>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="E12" s="1"/>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="5"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C14" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="5"/>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="5"/>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="5"/>
+    </row>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="5"/>
+    </row>
+    <row r="18" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="E18" s="1"/>
+      <c r="F18" s="5"/>
+    </row>
+    <row r="19" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="E19" s="1"/>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="E20" s="1"/>
+      <c r="F20" s="5"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>